--- a/_build/escenarios_logit_rstars.xlsx
+++ b/_build/escenarios_logit_rstars.xlsx
@@ -1,64 +1,231 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebasaluuclm-my.sharepoint.com/personal/miguelangel_tarancon_uclm_es/Documents/Documentos/curso/Cursos de Datos/New Book/RStars-book/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_2B4CA177D47D02DEE72FFC57435D2EBA3504EE2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63E41C4B-91EE-4324-B3C3-1D964F2C6636}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Inicio" sheetId="2" r:id="rId1"/>
+    <sheet name="Variables" sheetId="3" r:id="rId2"/>
+    <sheet name="Escenarios" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+  <si>
+    <t>ESCENARIO</t>
+  </si>
+  <si>
+    <t>SOLVENCIA</t>
+  </si>
+  <si>
+    <t>IPUNT</t>
+  </si>
+  <si>
+    <t>TINCID</t>
+  </si>
+  <si>
+    <t>IFIDE</t>
+  </si>
+  <si>
+    <t>FLOTA</t>
+  </si>
+  <si>
+    <t>RUTAS</t>
+  </si>
+  <si>
+    <t>EXPERIENCIA</t>
+  </si>
+  <si>
+    <t>EFLO</t>
+  </si>
+  <si>
+    <t>Candidata fuerte</t>
+  </si>
+  <si>
+    <t>RENOVADA</t>
+  </si>
+  <si>
+    <t>Candidata débil</t>
+  </si>
+  <si>
+    <t>ANTIGUA</t>
+  </si>
+  <si>
+    <t>Candidata media</t>
+  </si>
+  <si>
+    <t>MADURA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AVISO:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Esta base de datos, así como sus elementos y datos, son totalmente ficticios.</t>
+    </r>
+  </si>
+  <si>
+    <t>Los nombres de las empresas y sus sedes se han inspirado en distintas fuentes de la filmografía de ciencia ficción,</t>
+  </si>
+  <si>
+    <t>con intereses puramente didácticos.</t>
+  </si>
+  <si>
+    <t>* Imagen generada con IA.</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Unidades</t>
+  </si>
+  <si>
+    <t>Estado de renovación de la flota de cargueros.</t>
+  </si>
+  <si>
+    <t>Categórico (RENOVADA, MADURA, ANTIGUA)</t>
+  </si>
+  <si>
+    <t>Capacidad de la empresa para cubrir sus obligaciones financieras a largo plazo.</t>
+  </si>
+  <si>
+    <t>Índice (sin unidades)</t>
+  </si>
+  <si>
+    <t>Número de cargueros espaciales operativos.</t>
+  </si>
+  <si>
+    <t>Enteros</t>
+  </si>
+  <si>
+    <t>Número de rutas interestelares gestionadas por la empresa.</t>
+  </si>
+  <si>
+    <t>Índice de fidelización de los clientes.</t>
+  </si>
+  <si>
+    <t>Índice de puntualidad de la compañía en sus entregas.</t>
+  </si>
+  <si>
+    <t>Índice (0-100)</t>
+  </si>
+  <si>
+    <t>Tasa de incidencias registradas por cada 1.000 años-luz operados.</t>
+  </si>
+  <si>
+    <t>Incidencias / 1.000 años-luz</t>
+  </si>
+  <si>
+    <t>Años de experiencia de la compañía en rutas intergalácticas similares a la solicitada.</t>
+  </si>
+  <si>
+    <t>Años</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-        <bgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="5" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -67,112 +234,382 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Century Gothic"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4472C4"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>73342</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>12247</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2491096B-F580-4F7E-BE43-510039EC9BFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="201930" y="1019175"/>
+          <a:ext cx="7148512" cy="3968932"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{58A0F9E9-2020-44CA-9A59-B65FE4810E73}" name="Tabla1" displayName="Tabla1" ref="A1:C9" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+  <autoFilter ref="A1:C9" xr:uid="{58A0F9E9-2020-44CA-9A59-B65FE4810E73}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{58E05FA4-545D-407B-992B-206FD05AEA19}" name="Variable" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{7E77F8B2-620D-41AC-A976-672702576456}" name="Descripción" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B70DC565-23A4-4D06-AC6E-48DFC1E60B1D}" name="Unidades" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,169 +896,296 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2DFEE1E-9579-4943-894B-517CF1265706}">
+  <dimension ref="B1:B28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="10.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ESCENARIO</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SOLVENCIA</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>IPUNT</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TINCID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>IFIDE</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FLOTA</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>RUTAS</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>EXPERIENCIA</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>EFLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Candidata fuerte</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+    <row r="1" spans="2:2" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="2:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="2:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{185C64C7-B38A-42EA-A561-C7D95CC27E98}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="88.77734375" customWidth="1"/>
+    <col min="3" max="3" width="59.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="11">
         <v>210</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="11">
         <v>78</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="11">
         <v>2.5</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="11">
         <v>50</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="11">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="11">
         <v>600</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="11">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Candidata débil</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
+      <c r="I2" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7">
         <v>145</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7">
         <v>40</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="7">
         <v>14</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7">
         <v>25</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7">
         <v>8</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="7">
         <v>150</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7">
         <v>2</v>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Candidata media</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+      <c r="I3" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="11">
         <v>180</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="11">
         <v>60</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="11">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="11">
         <v>40</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="11">
         <v>15</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="11">
         <v>350</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="11">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="I4" s="13" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
